--- a/feasibility_outputs/profile_master_review_resolution/master_review_resolution_template.xlsx
+++ b/feasibility_outputs/profile_master_review_resolution/master_review_resolution_template.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
